--- a/backend/output/template/测试用例HTTP请求步骤数据源模板.xlsx
+++ b/backend/output/template/测试用例HTTP请求步骤数据源模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/Fastapi-Vue/Krun/backend/output/download/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/Fastapi-Vue/KeenRunner/backend/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB816058-72C9-5F48-A474-2922F2F76C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D26B49B-D0D2-5641-97F3-B65137B73BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="48200" yWindow="7360" windowWidth="28580" windowHeight="17440" xr2:uid="{B4CDD553-F6E2-E74E-A789-E7CE3B2875FD}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>场景1名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,7 +57,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ASSERT</t>
+    <t>ASSERT_HEAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASSERT_BODY</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -127,11 +131,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,6 +453,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C401589C-A87D-0D49-B83B-478A1235A391}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="1" width="12.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1"/>
@@ -483,15 +490,15 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -503,7 +510,9 @@
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -522,7 +531,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
